--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_65_R7.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_65_R7.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4927</v>
+        <v>5.9548</v>
       </c>
       <c r="E2" t="n">
-        <v>4.819</v>
+        <v>5.2475</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6737</v>
+        <v>0.7073</v>
       </c>
       <c r="G2" t="n">
         <v>2.2408</v>
@@ -610,13 +610,13 @@
         <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7481</v>
+        <v>-0.286</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7468</v>
+        <v>-0.3183</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0013</v>
+        <v>0.0323</v>
       </c>
       <c r="V2" t="n">
         <v>2.1444</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. HERNANGOMEZ</t>
+          <t>C. OSMAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2795</v>
+        <v>3.2975</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4962</v>
+        <v>3.3522</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7834</v>
+        <v>-0.0547</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.6002</v>
+        <v>-1.0634</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.7575</v>
+        <v>-1.9735</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1573</v>
+        <v>0.9101</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1203</v>
+        <v>0.8280999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5026</v>
+        <v>0.3298</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.6229</v>
+        <v>0.4983</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4799</v>
+        <v>-1.8915</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.2601</v>
+        <v>-2.3032</v>
       </c>
       <c r="O3" t="n">
-        <v>1.7802</v>
+        <v>0.4118</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8556</v>
+        <v>3.2473</v>
       </c>
       <c r="S3" t="n">
-        <v>4.4185</v>
+        <v>0.8944</v>
       </c>
       <c r="T3" t="n">
-        <v>4.0108</v>
+        <v>0.5548</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4077</v>
+        <v>0.3396</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3943</v>
+        <v>2.5387</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3943</v>
+        <v>4.2888</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. YURTSEVEN</t>
+          <t>J. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5243</v>
+        <v>2.6756</v>
       </c>
       <c r="E4" t="n">
-        <v>7.0273</v>
+        <v>1.0938</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.503</v>
+        <v>1.5817</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.8769</v>
+        <v>-0.6002</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2847</v>
+        <v>-0.7575</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5921</v>
+        <v>0.1573</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5861</v>
+        <v>-0.1203</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4389</v>
+        <v>1.5026</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1472</v>
+        <v>-1.6229</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.463</v>
+        <v>-0.4799</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.7236</v>
+        <v>-2.2601</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7393999999999999</v>
+        <v>1.7802</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="S4" t="n">
-        <v>6.3343</v>
+        <v>1.8145</v>
       </c>
       <c r="T4" t="n">
-        <v>5.2452</v>
+        <v>1.6085</v>
       </c>
       <c r="U4" t="n">
-        <v>1.089</v>
+        <v>0.206</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.8608</v>
+        <v>-0.3943</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3558</v>
+        <v>-0.3943</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3291</v>
+        <v>1.4299</v>
       </c>
       <c r="E5" t="n">
         <v>0.9262</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4029</v>
+        <v>0.5037</v>
       </c>
       <c r="G5" t="n">
         <v>1.3365</v>
@@ -844,13 +844,13 @@
         <v>0.232</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2394</v>
+        <v>-0.1386</v>
       </c>
       <c r="T5" t="n">
         <v>-0.1494</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0901</v>
+        <v>0.0108</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. OSMAN</t>
+          <t>K. NUNN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2267</v>
+        <v>1.3168</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0797</v>
+        <v>-0.1844</v>
       </c>
       <c r="F6" t="n">
-        <v>0.147</v>
+        <v>1.5013</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.0634</v>
+        <v>-0.9664</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.9735</v>
+        <v>-5.1588</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9101</v>
+        <v>4.1924</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8280999999999999</v>
+        <v>-0.0434</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3298</v>
+        <v>-3.1917</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4983</v>
+        <v>3.1483</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8915</v>
+        <v>-0.923</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.3032</v>
+        <v>-1.9671</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4118</v>
+        <v>1.0441</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>3.2473</v>
+        <v>2.3195</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1764</v>
+        <v>1.1235</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.7177</v>
+        <v>1.0187</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5412</v>
+        <v>0.1048</v>
       </c>
       <c r="V6" t="n">
-        <v>2.5387</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>4.2888</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.7501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. MITOGLOU</t>
+          <t>O. YURTSEVEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1758</v>
+        <v>1.0042</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3539</v>
+        <v>4.0785</v>
       </c>
       <c r="F7" t="n">
-        <v>1.178</v>
+        <v>-3.0743</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.702</v>
+        <v>-0.8769</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2172</v>
+        <v>-0.2847</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5153</v>
+        <v>-0.5921</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.3058</v>
+        <v>1.5861</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9845</v>
+        <v>1.4389</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.3213</v>
+        <v>0.1472</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6039</v>
+        <v>-2.463</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2327</v>
+        <v>-1.7236</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8366</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9278</v>
+        <v>2.0876</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3141</v>
+        <v>2.8141</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0395</v>
+        <v>2.2964</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3536</v>
+        <v>0.5177</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0722</v>
+        <v>-1.8608</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0722</v>
+        <v>1.3558</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-3.2166</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. NUNN</t>
+          <t>J. GRANT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6444</v>
+        <v>0.4227</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9104</v>
+        <v>-1.4101</v>
       </c>
       <c r="F8" t="n">
-        <v>1.266</v>
+        <v>1.8328</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9664</v>
+        <v>-0.7529</v>
       </c>
       <c r="H8" t="n">
-        <v>-5.1588</v>
+        <v>-1.1979</v>
       </c>
       <c r="I8" t="n">
-        <v>4.1924</v>
+        <v>0.4451</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0434</v>
+        <v>-1.1667</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.1917</v>
+        <v>0.222</v>
       </c>
       <c r="L8" t="n">
-        <v>3.1483</v>
+        <v>-1.3887</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.923</v>
+        <v>0.4139</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.9671</v>
+        <v>-1.4199</v>
       </c>
       <c r="O8" t="n">
-        <v>1.0441</v>
+        <v>1.8337</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3195</v>
+        <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8377</v>
+        <v>0.9436</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7073</v>
+        <v>0.9164</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1305</v>
+        <v>0.0272</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. HOLMES</t>
+          <t>K. MITOGLOU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7232</v>
+        <v>-0.1616</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2062</v>
+        <v>-1.4404</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9294</v>
+        <v>1.2788</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4075</v>
+        <v>-0.702</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2904</v>
+        <v>-1.2172</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1171</v>
+        <v>0.5153</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7186</v>
+        <v>-1.3058</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5714</v>
+        <v>-0.9845</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1472</v>
+        <v>-0.3213</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1261</v>
+        <v>0.6039</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8618</v>
+        <v>-0.2327</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2643</v>
+        <v>0.8366</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6959</v>
+        <v>-0.232</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0606</v>
+        <v>-0.2998</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4876</v>
+        <v>-0.047</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.427</v>
+        <v>-0.2528</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0722</v>
+        <v>1.0722</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. SLOUKAS</t>
+          <t>R. HOLMES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4818</v>
+        <v>-1.0532</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1144</v>
+        <v>0.8091</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5962</v>
+        <v>-1.8622</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.391</v>
+        <v>-0.4075</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.3336</v>
+        <v>-0.2904</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0574</v>
+        <v>-0.1171</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3865</v>
+        <v>0.7186</v>
       </c>
       <c r="K10" t="n">
-        <v>0.39</v>
+        <v>0.5714</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0035</v>
+        <v>0.1472</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.7775</v>
+        <v>-1.1261</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.7236</v>
+        <v>-0.8618</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0539</v>
+        <v>-0.2643</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6269</v>
+        <v>-0.2693</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1845</v>
+        <v>0.0905</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4424</v>
+        <v>-0.3598</v>
       </c>
       <c r="V10" t="n">
-        <v>1.0722</v>
+        <v>-1.0722</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. GRANT</t>
+          <t>K. SLOUKAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8081</v>
+        <v>-1.1212</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.372</v>
+        <v>0.3071</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5639</v>
+        <v>-1.4282</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7529</v>
+        <v>-2.391</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1979</v>
+        <v>-1.3336</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4451</v>
+        <v>-1.0574</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1667</v>
+        <v>0.3865</v>
       </c>
       <c r="K11" t="n">
-        <v>0.222</v>
+        <v>0.39</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3887</v>
+        <v>-0.0035</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4139</v>
+        <v>-2.7775</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.4199</v>
+        <v>-1.7236</v>
       </c>
       <c r="O11" t="n">
-        <v>1.8337</v>
+        <v>-1.0539</v>
       </c>
       <c r="P11" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2871</v>
+        <v>-0.2662</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0455</v>
+        <v>0.0081</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2416</v>
+        <v>-0.2743</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>13.019</v>
+        <v>13.7655</v>
       </c>
       <c r="E12" t="n">
-        <v>12.0327</v>
+        <v>12.7795</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9862999999999997</v>
+        <v>0.9862000000000002</v>
       </c>
       <c r="G12" t="n">
         <v>-4.183</v>
@@ -1381,22 +1381,22 @@
         <v>2.0588</v>
       </c>
       <c r="P12" t="n">
-        <v>8.118399999999999</v>
+        <v>8.118400000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-8.118499999999999</v>
+        <v>-8.118500000000001</v>
       </c>
       <c r="R12" t="n">
         <v>16.2367</v>
       </c>
       <c r="S12" t="n">
-        <v>5.5837</v>
+        <v>6.3302</v>
       </c>
       <c r="T12" t="n">
-        <v>5.2319</v>
+        <v>5.978699999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3514</v>
+        <v>0.3515</v>
       </c>
       <c r="V12" t="n">
         <v>3.5002</v>
@@ -1405,7 +1405,7 @@
         <v>8.750500000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.2503</v>
+        <v>-5.250300000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.7686</v>
+        <v>4.7812</v>
       </c>
       <c r="E13" t="n">
-        <v>6.5954</v>
+        <v>4.9441</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1732</v>
+        <v>-0.1629</v>
       </c>
       <c r="G13" t="n">
         <v>4.4285</v>
@@ -1468,13 +1468,13 @@
         <v>1.3917</v>
       </c>
       <c r="S13" t="n">
-        <v>2.0876</v>
+        <v>0.1002</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1824</v>
+        <v>0.5311</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0949</v>
+        <v>-0.4309</v>
       </c>
       <c r="V13" t="n">
         <v>0.2525</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.9093</v>
+        <v>1.875</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7386</v>
+        <v>1.5027</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1707</v>
+        <v>0.3723</v>
       </c>
       <c r="G14" t="n">
         <v>1.5245</v>
@@ -1546,13 +1546,13 @@
         <v>0.232</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3822</v>
+        <v>0.3479</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6449</v>
+        <v>0.409</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2627</v>
+        <v>-0.0611</v>
       </c>
       <c r="V14" t="n">
         <v>0.9304</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0422</v>
+        <v>0.2946</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7939000000000001</v>
+        <v>1.0298</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8361</v>
+        <v>-0.7353</v>
       </c>
       <c r="G15" t="n">
         <v>0.3545</v>
@@ -1624,13 +1624,13 @@
         <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1647</v>
+        <v>0.172</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0272</v>
+        <v>0.2087</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1375</v>
+        <v>-0.0367</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. HOARD</t>
+          <t>W. RAYMAN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3274</v>
+        <v>-0.165</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8454</v>
+        <v>-1.7563</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.1728</v>
+        <v>1.5913</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3136</v>
+        <v>-1.5468</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6615</v>
+        <v>-0.0612</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3478</v>
+        <v>-1.4856</v>
       </c>
       <c r="J16" t="n">
-        <v>3.0478</v>
+        <v>-2.2046</v>
       </c>
       <c r="K16" t="n">
-        <v>2.8638</v>
+        <v>-0.6687</v>
       </c>
       <c r="L16" t="n">
-        <v>0.184</v>
+        <v>-1.5359</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7342</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2023</v>
+        <v>0.6075</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5319</v>
+        <v>0.0502</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7982</v>
+        <v>0.9179</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1123</v>
+        <v>0.4483</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3141</v>
+        <v>0.4696</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.0026</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>W. RAYMAN</t>
+          <t>J. HOARD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6876</v>
+        <v>-0.645</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.3461</v>
+        <v>2.4351</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6585</v>
+        <v>-3.0802</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.5468</v>
+        <v>1.3136</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0612</v>
+        <v>1.6615</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.4856</v>
+        <v>-0.3478</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.2046</v>
+        <v>3.0478</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6687</v>
+        <v>2.8638</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.5359</v>
+        <v>0.184</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6578000000000001</v>
+        <v>-1.7342</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6075</v>
+        <v>-1.2023</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0502</v>
+        <v>-0.5319</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3954</v>
+        <v>-1.1158</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1415</v>
+        <v>-0.5226</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5368000000000001</v>
+        <v>-0.5933</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-2.0026</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3667</v>
+        <v>-1.2152</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3586</v>
+        <v>-0.2406</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0082</v>
+        <v>-0.9746</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1672</v>
@@ -1858,13 +1858,13 @@
         <v>0.232</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2175</v>
+        <v>-0.0659</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2987</v>
+        <v>-0.1808</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0813</v>
+        <v>0.1149</v>
       </c>
       <c r="V18" t="n">
         <v>-1.214</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0632</v>
+        <v>-1.6764</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2815</v>
+        <v>0.3995</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.3448</v>
+        <v>-2.0759</v>
       </c>
       <c r="G19" t="n">
         <v>1.0048</v>
@@ -1936,13 +1936,13 @@
         <v>0.232</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9805</v>
+        <v>-0.5937</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2161</v>
+        <v>-0.0982</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7644</v>
+        <v>-0.4955</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.1806</v>
+        <v>-2.6079</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.4096</v>
+        <v>-2.9378</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2291</v>
+        <v>0.3299</v>
       </c>
       <c r="G20" t="n">
         <v>-0.5311</v>
@@ -2014,13 +2014,13 @@
         <v>0.232</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3299</v>
+        <v>0.2427</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2161</v>
+        <v>0.2557</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1138</v>
+        <v>-0.013</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.3753</v>
+        <v>-4.0887</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.15</v>
+        <v>-2.7961</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2253</v>
+        <v>-1.2926</v>
       </c>
       <c r="G21" t="n">
         <v>-0.0308</v>
@@ -2092,13 +2092,13 @@
         <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.0972</v>
+        <v>-1.8106</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8883</v>
+        <v>-0.5344</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.2089</v>
+        <v>-1.2762</v>
       </c>
       <c r="V21" t="n">
         <v>0.5361</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>O. BRISSETT</t>
+          <t>T. BLATT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.7284</v>
+        <v>-4.2863</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2208</v>
+        <v>-2.9619</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.9492</v>
+        <v>-1.3245</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.4648</v>
+        <v>0.2978</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.8425</v>
+        <v>0.3916</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6223</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2911</v>
+        <v>1.0204</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.8298</v>
+        <v>1.5293</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5386</v>
+        <v>-0.5089</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.1737</v>
+        <v>-0.7226</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0127</v>
+        <v>-1.1377</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1609</v>
+        <v>0.415</v>
       </c>
       <c r="P22" t="n">
+        <v>-2.5515</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-3.4793</v>
+      </c>
+      <c r="R22" t="n">
         <v>0.9278</v>
       </c>
-      <c r="Q22" t="n">
-        <v>-0.232</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.1598</v>
-      </c>
       <c r="S22" t="n">
-        <v>-1.1887</v>
+        <v>-2.0326</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4604</v>
+        <v>-0.503</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.6491</v>
+        <v>-1.5296</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.0026</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2836</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.2862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T. BLATT</t>
+          <t>O. BRISSETT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.9255</v>
+        <v>-5.2852</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1978</v>
+        <v>-0.6048</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7277</v>
+        <v>-4.6804</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2978</v>
+        <v>-2.4648</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3916</v>
+        <v>-1.8425</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.6223</v>
       </c>
       <c r="J23" t="n">
-        <v>1.0204</v>
+        <v>-0.2911</v>
       </c>
       <c r="K23" t="n">
-        <v>1.5293</v>
+        <v>-0.8298</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5089</v>
+        <v>0.5386</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7226</v>
+        <v>-2.1737</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1377</v>
+        <v>-1.0127</v>
       </c>
       <c r="O23" t="n">
-        <v>0.415</v>
+        <v>-1.1609</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.5515</v>
+        <v>0.9278</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.4793</v>
+        <v>-0.232</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.6718</v>
+        <v>-1.7456</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7389</v>
+        <v>-0.3653</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.9329</v>
+        <v>-1.3803</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-2.0026</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="24">
@@ -2281,22 +2281,22 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-13.019</v>
+        <v>-13.0189</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.9865000000000004</v>
+        <v>-0.9863</v>
       </c>
       <c r="F24" t="n">
-        <v>-12.0326</v>
+        <v>-12.0329</v>
       </c>
       <c r="G24" t="n">
-        <v>4.182999999999999</v>
+        <v>4.183</v>
       </c>
       <c r="H24" t="n">
-        <v>8.649800000000001</v>
+        <v>8.649799999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.466900000000001</v>
+        <v>-4.4669</v>
       </c>
       <c r="J24" t="n">
         <v>10.3515</v>
@@ -2317,7 +2317,7 @@
         <v>-2.4081</v>
       </c>
       <c r="P24" t="n">
-        <v>-8.118300000000001</v>
+        <v>-8.1183</v>
       </c>
       <c r="Q24" t="n">
         <v>-16.2368</v>
@@ -2326,13 +2326,13 @@
         <v>8.118499999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.5833</v>
+        <v>-5.5835</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3513999999999999</v>
+        <v>-0.3514999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-5.232</v>
+        <v>-5.2321</v>
       </c>
       <c r="V24" t="n">
         <v>-3.5002</v>
@@ -2341,7 +2341,7 @@
         <v>5.2503</v>
       </c>
       <c r="X24" t="n">
-        <v>-8.750500000000001</v>
+        <v>-8.750499999999999</v>
       </c>
     </row>
   </sheetData>
